--- a/EndResult/200m Butterfly.xlsx
+++ b/EndResult/200m Butterfly.xlsx
@@ -1187,12 +1187,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.28,14</t>
+          <t>2.28,06</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.05.2016</t>
+          <t>14.06.2015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
